--- a/data/trans_bre/P16-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 18,78</t>
+          <t>11,5; 18,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,77; 16,6</t>
+          <t>9,73; 16,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 20,1</t>
+          <t>12,19; 20,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 17,07</t>
+          <t>7,66; 17,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 32,07</t>
+          <t>18,01; 32,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,21; 23,92</t>
+          <t>13,0; 24,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,42; 31,04</t>
+          <t>17,34; 30,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 25,44</t>
+          <t>10,13; 25,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,42; 19,01</t>
+          <t>12,67; 19,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,45; 23,27</t>
+          <t>16,53; 23,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 16,74</t>
+          <t>10,03; 16,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 34,6</t>
+          <t>11,16; 33,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,81; 65,85</t>
+          <t>39,73; 67,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,16; 57,93</t>
+          <t>37,85; 57,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,29; 39,35</t>
+          <t>22,03; 38,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,52; 110,06</t>
+          <t>23,83; 103,28</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,03; 23,74</t>
+          <t>11,02; 23,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,44; 24,67</t>
+          <t>11,53; 24,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 16,05</t>
+          <t>4,06; 16,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 10,71</t>
+          <t>-0,09; 11,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,3; 79,8</t>
+          <t>29,67; 78,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 65,69</t>
+          <t>26,38; 66,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,38; 38,25</t>
+          <t>8,61; 41,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 21,91</t>
+          <t>-0,11; 23,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,7; 20,48</t>
+          <t>15,68; 20,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,37; 21,91</t>
+          <t>17,39; 22,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 17,56</t>
+          <t>12,74; 17,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,15; 29,62</t>
+          <t>11,03; 30,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,43; 52,27</t>
+          <t>37,4; 52,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,47; 44,65</t>
+          <t>33,52; 45,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 36,57</t>
+          <t>24,96; 36,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 76,89</t>
+          <t>20,96; 75,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>14,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 18,95</t>
+          <t>11,6; 19,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 16,77</t>
+          <t>9,72; 16,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,19; 20,15</t>
+          <t>12,35; 20,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 17,0</t>
+          <t>10,41; 19,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 32,32</t>
+          <t>18,28; 32,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 24,05</t>
+          <t>13,23; 24,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 30,68</t>
+          <t>17,35; 31,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 25,25</t>
+          <t>14,62; 30,48</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,47</t>
+          <t>9,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 19,11</t>
+          <t>12,36; 19,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,53; 23,14</t>
+          <t>16,7; 23,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,45</t>
+          <t>10,22; 16,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 33,21</t>
+          <t>6,87; 13,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,73; 67,28</t>
+          <t>38,58; 66,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,85; 57,33</t>
+          <t>38,13; 58,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 38,56</t>
+          <t>22,28; 38,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,83; 103,28</t>
+          <t>13,85; 28,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>5,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 23,67</t>
+          <t>11,31; 23,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 24,13</t>
+          <t>11,19; 24,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 16,95</t>
+          <t>3,92; 15,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 11,24</t>
+          <t>-0,51; 10,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,67; 78,69</t>
+          <t>31,32; 76,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,38; 66,39</t>
+          <t>24,8; 66,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 41,61</t>
+          <t>8,22; 37,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 23,16</t>
+          <t>-0,68; 20,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,94</t>
+          <t>11,04</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,45</t>
+          <t>15,47; 20,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 22,21</t>
+          <t>17,41; 22,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 17,57</t>
+          <t>12,72; 17,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 30,16</t>
+          <t>8,65; 13,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,31</t>
+          <t>37,26; 52,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,52; 45,61</t>
+          <t>33,55; 44,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,96; 36,44</t>
+          <t>24,77; 36,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,96; 75,6</t>
+          <t>16,17; 26,41</t>
         </is>
       </c>
     </row>
